--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -71,13 +71,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>10</t>
+    <t>11</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>edcce0c</t>
+    <t>348580a</t>
   </si>
   <si>
     <t>Branch</t>
@@ -89,7 +89,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 11:28:17 UTC</t>
+    <t>2026-06-23 12:11:26 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>
@@ -104,7 +104,7 @@
     <t>Grand Pass Rate</t>
   </si>
   <si>
-    <t>52.4%</t>
+    <t>67.8%</t>
   </si>
   <si>
     <t>Security Risk Score</t>
@@ -650,7 +650,7 @@
         <v>26</v>
       </c>
       <c r="B6">
-        <v>836</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -658,7 +658,7 @@
         <v>27</v>
       </c>
       <c r="B7">
-        <v>438</v>
+        <v>838</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="33">
   <si>
     <t>Testing Tier</t>
   </si>
@@ -47,6 +47,9 @@
     <t>100.0%</t>
   </si>
   <si>
+    <t>⚙️ Backend Service Tests</t>
+  </si>
+  <si>
     <t>🛡️ Backend Security Scan</t>
   </si>
   <si>
@@ -71,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>11</t>
+    <t>12</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>348580a</t>
+    <t>cfbb4d3</t>
   </si>
   <si>
     <t>Branch</t>
@@ -89,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 12:11:26 UTC</t>
+    <t>2026-06-23 13:25:14 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>
@@ -104,7 +107,7 @@
     <t>Grand Pass Rate</t>
   </si>
   <si>
-    <t>67.8%</t>
+    <t>70.1%</t>
   </si>
   <si>
     <t>Security Risk Score</t>
@@ -484,10 +487,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
@@ -558,39 +561,59 @@
       <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" t="s">
-        <v>12</v>
+      <c r="B4">
+        <v>400</v>
       </c>
       <c r="C4">
-        <v>30</v>
+        <v>400</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5">
-        <v>6</v>
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6">
+        <v>100</v>
+      </c>
+      <c r="C6">
+        <v>100</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6" t="s">
         <v>10</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F6" t="s">
         <v>8</v>
       </c>
     </row>
@@ -607,63 +630,63 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B6">
-        <v>1236</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B7">
-        <v>838</v>
+        <v>932</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B8">
         <v>9</v>
@@ -671,18 +694,18 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>12</t>
+    <t>14</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>cfbb4d3</t>
+    <t>3eb8262</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 13:25:14 UTC</t>
+    <t>2026-06-23 13:46:16 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>14</t>
+    <t>15</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>3eb8262</t>
+    <t>0bdfd4b</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 13:46:16 UTC</t>
+    <t>2026-06-23 13:54:24 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>15</t>
+    <t>16</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>0bdfd4b</t>
+    <t>e40a5d4</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 13:54:24 UTC</t>
+    <t>2026-06-23 14:02:13 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>16</t>
+    <t>17</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>e40a5d4</t>
+    <t>d1d53d0</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 14:02:13 UTC</t>
+    <t>2026-06-23 14:24:15 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>17</t>
+    <t>18</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>d1d53d0</t>
+    <t>04fd2d2</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 14:24:15 UTC</t>
+    <t>2026-06-23 14:34:11 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>18</t>
+    <t>19</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>04fd2d2</t>
+    <t>af530d5</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 14:34:11 UTC</t>
+    <t>2026-06-23 14:55:37 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>19</t>
+    <t>20</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>af530d5</t>
+    <t>a38f0ce</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 14:55:37 UTC</t>
+    <t>2026-06-23 15:17:03 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>20</t>
+    <t>21</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>a38f0ce</t>
+    <t>6a5e7ca</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 15:17:03 UTC</t>
+    <t>2026-06-23 15:24:28 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>21</t>
+    <t>22</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>6a5e7ca</t>
+    <t>f8042b0</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 15:24:28 UTC</t>
+    <t>2026-06-23 15:39:14 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>22</t>
+    <t>23</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>f8042b0</t>
+    <t>19701a0</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 15:39:14 UTC</t>
+    <t>2026-06-23 15:46:01 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,7 +74,7 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>23</t>
+    <t>24</t>
   </si>
   <si>
     <t>Commit SHA</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-23 15:46:01 UTC</t>
+    <t>2026-06-24 03:38:33 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>24</t>
+    <t>25</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>19701a0</t>
+    <t>f6dc91b</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-24 03:38:33 UTC</t>
+    <t>2026-06-24 04:45:16 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>25</t>
+    <t>26</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>f6dc91b</t>
+    <t>1b19601</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-24 04:45:16 UTC</t>
+    <t>2026-06-30 08:41:47 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>26</t>
+    <t>27</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>1b19601</t>
+    <t>9a48722</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-30 08:41:47 UTC</t>
+    <t>2026-06-30 13:27:23 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>27</t>
+    <t>28</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>9a48722</t>
+    <t>7bb6a7a</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-30 13:27:23 UTC</t>
+    <t>2026-06-30 13:36:22 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>28</t>
+    <t>29</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>7bb6a7a</t>
+    <t>c744b19</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-30 13:36:22 UTC</t>
+    <t>2026-06-30 13:43:58 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>29</t>
+    <t>30</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>c744b19</t>
+    <t>6c162b2</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-30 13:43:58 UTC</t>
+    <t>2026-06-30 13:51:01 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>30</t>
+    <t>31</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>6c162b2</t>
+    <t>4e802ad</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-30 13:51:01 UTC</t>
+    <t>2026-06-30 14:00:32 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>31</t>
+    <t>32</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>4e802ad</t>
+    <t>36ef16e</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-30 14:00:32 UTC</t>
+    <t>2026-06-30 14:26:07 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>32</t>
+    <t>34</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>36ef16e</t>
+    <t>16d388e</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-30 14:26:07 UTC</t>
+    <t>2026-06-30 14:32:49 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>34</t>
+    <t>36</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>16d388e</t>
+    <t>c0c6499</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-30 14:32:49 UTC</t>
+    <t>2026-06-30 14:40:34 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>36</t>
+    <t>37</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>c0c6499</t>
+    <t>69c8bfb</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-30 14:40:34 UTC</t>
+    <t>2026-06-30 14:50:50 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>37</t>
+    <t>38</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>69c8bfb</t>
+    <t>8620bea</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-30 14:50:50 UTC</t>
+    <t>2026-06-30 15:02:50 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>38</t>
+    <t>39</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>8620bea</t>
+    <t>bbf0a04</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-30 15:02:50 UTC</t>
+    <t>2026-06-30 15:17:13 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>39</t>
+    <t>41</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>bbf0a04</t>
+    <t>2e22a52</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-30 15:17:13 UTC</t>
+    <t>2026-06-30 15:26:17 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>41</t>
+    <t>42</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>2e22a52</t>
+    <t>bb12b5d</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-30 15:26:17 UTC</t>
+    <t>2026-06-30 17:25:42 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>42</t>
+    <t>43</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>bb12b5d</t>
+    <t>feb30ad</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-30 17:25:42 UTC</t>
+    <t>2026-06-30 17:40:24 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>43</t>
+    <t>44</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>feb30ad</t>
+    <t>dfc30c0</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-06-30 17:40:24 UTC</t>
+    <t>2026-06-30 17:51:33 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>45</t>
+    <t>46</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>6c3e421</t>
+    <t>f5c0ab7</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-20 04:32:35 UTC</t>
+    <t>2026-07-20 04:53:32 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>46</t>
+    <t>47</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>f5c0ab7</t>
+    <t>2dd4e06</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-20 04:53:32 UTC</t>
+    <t>2026-07-20 05:04:48 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>47</t>
+    <t>48</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>2dd4e06</t>
+    <t>a601b64</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-20 05:04:48 UTC</t>
+    <t>2026-07-20 05:16:47 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>48</t>
+    <t>49</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>a601b64</t>
+    <t>4642e1d</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-20 05:16:47 UTC</t>
+    <t>2026-07-20 05:22:59 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>49</t>
+    <t>50</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>4642e1d</t>
+    <t>6ff8f77</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-20 05:22:59 UTC</t>
+    <t>2026-07-20 05:29:23 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>50</t>
+    <t>51</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>6ff8f77</t>
+    <t>521b99b</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-20 05:29:23 UTC</t>
+    <t>2026-07-20 05:37:23 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>51</t>
+    <t>52</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>521b99b</t>
+    <t>44e8e58</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-20 05:37:23 UTC</t>
+    <t>2026-07-20 05:43:34 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>52</t>
+    <t>53</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>44e8e58</t>
+    <t>d05746b</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-20 05:43:34 UTC</t>
+    <t>2026-07-20 05:55:30 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>53</t>
+    <t>54</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>d05746b</t>
+    <t>c2b056c</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-20 05:55:30 UTC</t>
+    <t>2026-07-20 06:11:19 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>54</t>
+    <t>55</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>c2b056c</t>
+    <t>6166361</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-20 06:11:19 UTC</t>
+    <t>2026-07-20 06:18:53 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>55</t>
+    <t>56</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>6166361</t>
+    <t>ea04ba1</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-20 06:18:53 UTC</t>
+    <t>2026-07-20 11:18:12 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>56</t>
+    <t>57</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>ea04ba1</t>
+    <t>444b861</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-20 11:18:12 UTC</t>
+    <t>2026-07-20 11:32:20 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>57</t>
+    <t>58</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>444b861</t>
+    <t>2507a7b</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-20 11:32:20 UTC</t>
+    <t>2026-07-20 11:38:28 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>58</t>
+    <t>59</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>2507a7b</t>
+    <t>8511c2b</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-20 11:38:28 UTC</t>
+    <t>2026-07-20 15:19:49 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>59</t>
+    <t>60</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>8511c2b</t>
+    <t>0291447</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-20 15:19:49 UTC</t>
+    <t>2026-07-20 15:32:18 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -56,7 +56,7 @@
     <t>30 rules</t>
   </si>
   <si>
-    <t>4/100</t>
+    <t>15/100</t>
   </si>
   <si>
     <t>SECURE</t>
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>60</t>
+    <t>61</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>0291447</t>
+    <t>00ba088</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-20 15:32:18 UTC</t>
+    <t>2026-07-21 10:10:32 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>61</t>
+    <t>62</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>00ba088</t>
+    <t>536fb94</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-21 10:10:32 UTC</t>
+    <t>2026-07-21 10:38:35 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -56,7 +56,7 @@
     <t>30 rules</t>
   </si>
   <si>
-    <t>15/100</t>
+    <t>10/100</t>
   </si>
   <si>
     <t>SECURE</t>
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>62</t>
+    <t>63</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>536fb94</t>
+    <t>9c8f524</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-21 10:38:35 UTC</t>
+    <t>2026-07-21 11:01:58 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>63</t>
+    <t>64</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>9c8f524</t>
+    <t>ed920c1</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-21 11:01:58 UTC</t>
+    <t>2026-07-21 13:14:28 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>64</t>
+    <t>65</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>ed920c1</t>
+    <t>f0162ef</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-21 13:14:28 UTC</t>
+    <t>2026-07-21 13:49:07 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>65</t>
+    <t>66</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>f0162ef</t>
+    <t>c20f7b4</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-21 13:49:07 UTC</t>
+    <t>2026-07-21 13:59:36 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>66</t>
+    <t>67</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>c20f7b4</t>
+    <t>77d93ce</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-21 13:59:36 UTC</t>
+    <t>2026-07-21 14:19:04 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>67</t>
+    <t>68</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>77d93ce</t>
+    <t>14f8400</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-21 14:19:04 UTC</t>
+    <t>2026-07-21 14:28:34 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>68</t>
+    <t>69</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>14f8400</t>
+    <t>087f127</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-21 14:28:34 UTC</t>
+    <t>2026-07-21 14:42:45 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>69</t>
+    <t>70</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>087f127</t>
+    <t>6958884</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-21 14:42:45 UTC</t>
+    <t>2026-07-21 15:15:31 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>70</t>
+    <t>71</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>6958884</t>
+    <t>2d71144</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-21 15:15:31 UTC</t>
+    <t>2026-07-22 02:07:59 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>71</t>
+    <t>72</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>2d71144</t>
+    <t>a96e094</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-22 02:07:59 UTC</t>
+    <t>2026-07-22 02:52:52 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>72</t>
+    <t>73</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>a96e094</t>
+    <t>adc634e</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-22 02:52:52 UTC</t>
+    <t>2026-07-22 02:59:41 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>77</t>
+    <t>78</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>b0c83f8</t>
+    <t>6a5de8e</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-22 03:43:28 UTC</t>
+    <t>2026-07-22 03:49:57 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>80</t>
+    <t>81</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>e4fdde1</t>
+    <t>49466e1</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-22 04:17:37 UTC</t>
+    <t>2026-07-22 04:24:08 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -56,7 +56,7 @@
     <t>30 rules</t>
   </si>
   <si>
-    <t>10/100</t>
+    <t>11/100</t>
   </si>
   <si>
     <t>SECURE</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-22 04:24:08 UTC</t>
+    <t>2026-07-23 08:30:06 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -56,7 +56,7 @@
     <t>30 rules</t>
   </si>
   <si>
-    <t>11/100</t>
+    <t>16/100</t>
   </si>
   <si>
     <t>SECURE</t>
@@ -74,13 +74,13 @@
     <t>Build Number</t>
   </si>
   <si>
-    <t>81</t>
+    <t>82</t>
   </si>
   <si>
     <t>Commit SHA</t>
   </si>
   <si>
-    <t>49466e1</t>
+    <t>c1ecc81</t>
   </si>
   <si>
     <t>Branch</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-23 08:30:06 UTC</t>
+    <t>2026-07-30 09:28:47 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-30 09:28:47 UTC</t>
+    <t>2026-07-31 07:44:00 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>

--- a/reports/unified-summary.xlsx
+++ b/reports/unified-summary.xlsx
@@ -56,7 +56,7 @@
     <t>30 rules</t>
   </si>
   <si>
-    <t>16/100</t>
+    <t>29/100</t>
   </si>
   <si>
     <t>SECURE</t>
@@ -92,7 +92,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>2026-07-31 07:44:00 UTC</t>
+    <t>2026-08-09 03:17:32 UTC</t>
   </si>
   <si>
     <t>Grand Total Tests</t>
